--- a/Robot_BOM.xlsx
+++ b/Robot_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Federico\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E522B9-4E1E-4578-8F4E-8FDAE41DC0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE147E79-7A9B-434C-B302-11941678B98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <si>
     <t>Reference</t>
   </si>
@@ -151,33 +151,21 @@
     <t>C15, C16</t>
   </si>
   <si>
-    <t>https://www.aliexpress.com/w/wholesale-0805-capacitor-sample-book.html</t>
-  </si>
-  <si>
     <t>C12</t>
   </si>
   <si>
     <t>C6..C14, C17…</t>
   </si>
   <si>
-    <t>100nF 0805 (book)</t>
-  </si>
-  <si>
     <t>C1, C2</t>
   </si>
   <si>
-    <t>18pF 0805 (book)</t>
-  </si>
-  <si>
     <t>R4, R8, R9..R21</t>
   </si>
   <si>
     <t>10k 0805 (book)</t>
   </si>
   <si>
-    <t>https://www.aliexpress.com/w/wholesale-0805-resistor-sample-book.html</t>
-  </si>
-  <si>
     <t>R7, R10</t>
   </si>
   <si>
@@ -353,6 +341,18 @@
   </si>
   <si>
     <t>Nema 17 10:1 gearbox</t>
+  </si>
+  <si>
+    <t>100nF 50V 0805 (smd)</t>
+  </si>
+  <si>
+    <t>https://it.aliexpress.com/item/1005010243722146.html</t>
+  </si>
+  <si>
+    <t>18pF 50V 0805 (smd)</t>
+  </si>
+  <si>
+    <t>https://it.aliexpress.com/item/1005005504891922.html</t>
   </si>
 </sst>
 </file>
@@ -437,7 +437,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -457,28 +457,34 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -795,12 +801,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="A1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -898,8 +904,8 @@
       <c r="E6" s="3">
         <v>1.2</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>79</v>
+      <c r="F6" s="7" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -950,7 +956,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D9" s="3">
         <v>6.7</v>
@@ -978,7 +984,7 @@
       <c r="E10" s="3">
         <v>2</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -998,8 +1004,8 @@
       <c r="E11" s="3">
         <v>5.8</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>81</v>
+      <c r="F11" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1012,14 +1018,14 @@
       <c r="C12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="13">
         <v>20.190000000000001</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="13">
         <v>20.190000000000001</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>82</v>
+      <c r="F12" s="12" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1032,9 +1038,9 @@
       <c r="C13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="13"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="12"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1046,9 +1052,9 @@
       <c r="C14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="13"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="12"/>
     </row>
     <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -1066,8 +1072,8 @@
       <c r="E15" s="3">
         <v>9.18</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>83</v>
+      <c r="F15" s="7" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1078,7 +1084,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D16" s="3">
         <v>10.42</v>
@@ -1086,8 +1092,8 @@
       <c r="E16" s="3">
         <v>10.42</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>84</v>
+      <c r="F16" s="7" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -1098,7 +1104,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D17" s="3">
         <v>2.0499999999999998</v>
@@ -1106,8 +1112,8 @@
       <c r="E17" s="3">
         <v>2.0499999999999998</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>86</v>
+      <c r="F17" s="7" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -1118,7 +1124,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D18" s="3">
         <v>2</v>
@@ -1126,11 +1132,11 @@
       <c r="E18" s="3">
         <v>2</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F18" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>41</v>
       </c>
@@ -1138,7 +1144,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D19" s="3">
         <v>2</v>
@@ -1146,177 +1152,151 @@
       <c r="E19" s="3">
         <v>2</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F19" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2</v>
+      </c>
+      <c r="F20" s="16"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="B20" s="2">
-        <v>1</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" s="3">
-        <v>2</v>
-      </c>
-      <c r="E20" s="3">
-        <v>2</v>
-      </c>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="B21" s="2">
         <v>14</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="E21" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="2">
+        <v>2</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="3">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5</v>
+      </c>
+      <c r="F22" s="16"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="D21" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="2">
-        <v>2</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="B23" s="2">
         <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="3">
+        <v>40</v>
+      </c>
+      <c r="E23" s="3">
+        <v>40</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="12"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="E23" s="3">
-        <v>0.12</v>
-      </c>
-      <c r="F23" s="4" t="s">
+      <c r="B25" s="2">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="12"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="2">
-        <v>2</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="B26" s="2">
+        <v>2</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="12"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="2">
-        <v>1</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="B27" s="2">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="2">
-        <v>2</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="E26" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="2">
-        <v>1</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="E27" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>50</v>
-      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="16"/>
     </row>
     <row r="28" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B28" s="2">
         <v>2</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D28" s="3">
         <v>1</v>
@@ -1324,19 +1304,19 @@
       <c r="E28" s="3">
         <v>2</v>
       </c>
-      <c r="F28" s="9" t="s">
-        <v>94</v>
+      <c r="F28" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B29" s="2">
         <v>1</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D29" s="3">
         <v>2.91</v>
@@ -1344,19 +1324,19 @@
       <c r="E29" s="3">
         <v>2.91</v>
       </c>
-      <c r="F29" s="9" t="s">
-        <v>95</v>
+      <c r="F29" s="7" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B30" s="2">
         <v>2</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D30" s="3">
         <v>18</v>
@@ -1364,19 +1344,19 @@
       <c r="E30" s="3">
         <v>36</v>
       </c>
-      <c r="F30" s="9" t="s">
-        <v>96</v>
+      <c r="F30" s="7" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B31" s="2">
         <v>3</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D31" s="3">
         <v>9</v>
@@ -1384,19 +1364,19 @@
       <c r="E31" s="3">
         <v>27</v>
       </c>
-      <c r="F31" s="9" t="s">
-        <v>97</v>
+      <c r="F31" s="7" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B32" s="2">
         <v>1</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D32" s="3">
         <v>12</v>
@@ -1404,19 +1384,19 @@
       <c r="E32" s="3">
         <v>12</v>
       </c>
-      <c r="F32" s="9" t="s">
-        <v>99</v>
+      <c r="F32" s="7" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B33" s="2">
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D33" s="3">
         <v>7.3</v>
@@ -1424,19 +1404,19 @@
       <c r="E33" s="3">
         <v>44</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>105</v>
+      <c r="F33" s="7" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B34" s="2">
         <v>1</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D34" s="3">
         <v>21</v>
@@ -1444,19 +1424,19 @@
       <c r="E34" s="3">
         <v>21</v>
       </c>
-      <c r="F34" s="9" t="s">
-        <v>100</v>
+      <c r="F34" s="7" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B35" s="2">
         <v>1</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D35" s="3">
         <v>40</v>
@@ -1465,18 +1445,18 @@
         <v>40</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B36" s="2">
         <v>1</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D36" s="3">
         <v>5</v>
@@ -1484,19 +1464,19 @@
       <c r="E36" s="3">
         <v>5</v>
       </c>
-      <c r="F36" s="9" t="s">
-        <v>101</v>
+      <c r="F36" s="7" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B37" s="2">
         <v>1</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D37" s="3">
         <v>2</v>
@@ -1504,19 +1484,19 @@
       <c r="E37" s="3">
         <v>2</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>103</v>
+      <c r="F37" s="7" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B38" s="2">
         <v>1</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D38" s="3">
         <v>2.5</v>
@@ -1524,45 +1504,45 @@
       <c r="E38" s="3">
         <v>2.5</v>
       </c>
-      <c r="F38" s="9" t="s">
-        <v>102</v>
+      <c r="F38" s="7" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B39" s="14">
-        <v>2</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D39" s="15">
+      <c r="B39" s="8">
+        <v>2</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D39" s="9">
         <v>20</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="9">
         <v>40</v>
       </c>
-      <c r="F39" s="13" t="s">
-        <v>108</v>
+      <c r="F39" s="12" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B40" s="14">
-        <v>1</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D40" s="15">
+      <c r="B40" s="8">
+        <v>1</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D40" s="9">
         <v>18</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="9">
         <v>18</v>
       </c>
-      <c r="F40" s="13"/>
+      <c r="F40" s="12"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B42" s="5">
         <f>SUM(B3:B40)</f>
@@ -1572,18 +1552,21 @@
       <c r="D42" s="5"/>
       <c r="E42" s="6">
         <f>SUM(E5:E40)</f>
-        <v>327.29000000000002</v>
+        <v>376.28999999999996</v>
       </c>
       <c r="F42" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:F38" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="5">
+  <mergeCells count="8">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="E12:E14"/>
     <mergeCell ref="F39:F40"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -1600,29 +1583,24 @@
     <hyperlink ref="F18" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
     <hyperlink ref="F19" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
     <hyperlink ref="F21" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="F22" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="F23" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="F24" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="F25" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="F26" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="F27" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="F28" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="F29" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="F30" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="F31" r:id="rId24" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="F32" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="F33" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="F34" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="F35" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="F36" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="F37" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="F12" r:id="rId31" xr:uid="{E5B6C6DF-D092-4CB4-B021-0E0BE645ADD0}"/>
-    <hyperlink ref="F15" r:id="rId32" xr:uid="{ED22CB4C-DDFF-4375-A264-E3B547CB0576}"/>
-    <hyperlink ref="F38" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="F39" r:id="rId34" xr:uid="{FA956232-5F8F-497D-9C4F-BD1B630F2A6C}"/>
-    <hyperlink ref="F39:F40" r:id="rId35" display="https://it.aliexpress.com/item/1005010354201440.html" xr:uid="{39784570-9BED-4A28-B47E-382D59C4853A}"/>
+    <hyperlink ref="F23" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="F28" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="F29" r:id="rId17" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="F30" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="F31" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="F32" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="F33" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="F34" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="F35" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="F36" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="F37" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="F12" r:id="rId26" xr:uid="{E5B6C6DF-D092-4CB4-B021-0E0BE645ADD0}"/>
+    <hyperlink ref="F15" r:id="rId27" xr:uid="{ED22CB4C-DDFF-4375-A264-E3B547CB0576}"/>
+    <hyperlink ref="F38" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="F39" r:id="rId29" xr:uid="{FA956232-5F8F-497D-9C4F-BD1B630F2A6C}"/>
+    <hyperlink ref="F39:F40" r:id="rId30" display="https://it.aliexpress.com/item/1005010354201440.html" xr:uid="{39784570-9BED-4A28-B47E-382D59C4853A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId36"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId31"/>
 </worksheet>
 </file>
--- a/Robot_BOM.xlsx
+++ b/Robot_BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Federico\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE147E79-7A9B-434C-B302-11941678B98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04922FB-FEC0-49AC-90A1-8CCC9669B060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2895" yWindow="2895" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t>Reference</t>
   </si>
@@ -353,6 +353,12 @@
   </si>
   <si>
     <t>https://it.aliexpress.com/item/1005005504891922.html</t>
+  </si>
+  <si>
+    <t>1kg PETG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCB board </t>
   </si>
 </sst>
 </file>
@@ -789,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1540,21 +1546,49 @@
       </c>
       <c r="F40" s="12"/>
     </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B41" s="8">
+        <v>2</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D41" s="9">
+        <v>25</v>
+      </c>
+      <c r="E41" s="9">
+        <v>50</v>
+      </c>
+    </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+      <c r="B42" s="8">
+        <v>1</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" s="9">
+        <v>100</v>
+      </c>
+      <c r="E42" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B42" s="5">
-        <f>SUM(B3:B40)</f>
-        <v>94</v>
-      </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="6">
-        <f>SUM(E5:E40)</f>
-        <v>376.28999999999996</v>
-      </c>
-      <c r="F42" s="5"/>
+      <c r="B43" s="5">
+        <f>SUM(B3:B42)</f>
+        <v>97</v>
+      </c>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="6">
+        <f>SUM(E7:E42)</f>
+        <v>523.59</v>
+      </c>
+      <c r="F43" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:F38" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/Robot_BOM.xlsx
+++ b/Robot_BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Federico\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04922FB-FEC0-49AC-90A1-8CCC9669B060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4235EC-7347-4AAA-85C1-68F85142283D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2895" yWindow="2895" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1920" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -67,9 +67,6 @@
     <t>SN65HVD230</t>
   </si>
   <si>
-    <t>https://www.aliexpress.com/item/1005008251308592.html</t>
-  </si>
-  <si>
     <t>U11</t>
   </si>
   <si>
@@ -359,6 +356,9 @@
   </si>
   <si>
     <t xml:space="preserve">PCB board </t>
+  </si>
+  <si>
+    <t>https://it.aliexpress.com/item/1005006203720105.html</t>
   </si>
 </sst>
 </file>
@@ -870,7 +870,7 @@
       <c r="E4" s="3">
         <v>1.75</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -885,24 +885,24 @@
         <v>13</v>
       </c>
       <c r="D5" s="3">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="E5" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>14</v>
+        <v>3.8</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="D6" s="3">
         <v>1.2</v>
@@ -911,18 +911,18 @@
         <v>1.2</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" s="2">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="D7" s="3">
         <v>5.84</v>
@@ -931,18 +931,18 @@
         <v>5.84</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B8" s="2">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="D8" s="3">
         <v>3.5</v>
@@ -950,19 +950,19 @@
       <c r="E8" s="3">
         <v>3.5</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>22</v>
+      <c r="F8" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D9" s="3">
         <v>6.7</v>
@@ -971,38 +971,38 @@
         <v>6.7</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="2">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="3">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="D10" s="3">
-        <v>2</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="D11" s="3">
         <v>2.9</v>
@@ -1011,18 +1011,18 @@
         <v>5.8</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" s="13">
         <v>20.190000000000001</v>
@@ -1031,18 +1031,18 @@
         <v>20.190000000000001</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="2">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
@@ -1050,13 +1050,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
@@ -1064,13 +1064,13 @@
     </row>
     <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B15" s="2">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="D15" s="3">
         <v>9.18</v>
@@ -1079,18 +1079,18 @@
         <v>9.18</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D16" s="3">
         <v>10.42</v>
@@ -1099,18 +1099,18 @@
         <v>10.42</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="2">
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D17" s="3">
         <v>2.0499999999999998</v>
@@ -1119,38 +1119,38 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2">
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="D18" s="3">
-        <v>2</v>
-      </c>
-      <c r="E18" s="3">
-        <v>2</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" s="2">
         <v>2</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D19" s="3">
         <v>2</v>
@@ -1159,18 +1159,18 @@
         <v>2</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" s="2">
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D20" s="3">
         <v>2</v>
@@ -1182,13 +1182,13 @@
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="2">
         <v>14</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D21" s="3">
         <v>4.5</v>
@@ -1197,18 +1197,18 @@
         <v>4.5</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2">
         <v>2</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D22" s="3">
         <v>5</v>
@@ -1220,13 +1220,13 @@
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B23" s="2">
         <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D23" s="3">
         <v>40</v>
@@ -1235,18 +1235,18 @@
         <v>40</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="B24" s="2">
-        <v>2</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -1254,13 +1254,13 @@
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="2">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="B25" s="2">
-        <v>1</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -1268,13 +1268,13 @@
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="2">
+        <v>2</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B26" s="2">
-        <v>2</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -1282,13 +1282,13 @@
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="2">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="B27" s="2">
-        <v>1</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -1296,33 +1296,33 @@
     </row>
     <row r="28" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B28" s="2">
         <v>2</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3">
+        <v>2</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="D28" s="3">
-        <v>1</v>
-      </c>
-      <c r="E28" s="3">
-        <v>2</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="2">
+        <v>1</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="B29" s="2">
-        <v>1</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="D29" s="3">
         <v>2.91</v>
@@ -1331,18 +1331,18 @@
         <v>2.91</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="2">
+        <v>2</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B30" s="2">
-        <v>2</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D30" s="3">
         <v>18</v>
@@ -1351,18 +1351,18 @@
         <v>36</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B31" s="2">
         <v>3</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D31" s="3">
         <v>9</v>
@@ -1371,18 +1371,18 @@
         <v>27</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B32" s="2">
         <v>1</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D32" s="3">
         <v>12</v>
@@ -1391,18 +1391,18 @@
         <v>12</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B33" s="2">
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D33" s="3">
         <v>7.3</v>
@@ -1411,18 +1411,18 @@
         <v>44</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="2">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="B34" s="2">
-        <v>1</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="D34" s="3">
         <v>21</v>
@@ -1431,18 +1431,18 @@
         <v>21</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="2">
+        <v>1</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="B35" s="2">
-        <v>1</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="D35" s="3">
         <v>40</v>
@@ -1451,18 +1451,18 @@
         <v>40</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="2">
+        <v>1</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B36" s="2">
-        <v>1</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="D36" s="3">
         <v>5</v>
@@ -1471,18 +1471,18 @@
         <v>5</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B37" s="2">
         <v>1</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D37" s="3">
         <v>2</v>
@@ -1491,18 +1491,18 @@
         <v>2</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="2">
+        <v>1</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="B38" s="2">
-        <v>1</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="D38" s="3">
         <v>2.5</v>
@@ -1511,7 +1511,7 @@
         <v>2.5</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1519,7 +1519,7 @@
         <v>2</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D39" s="9">
         <v>20</v>
@@ -1528,7 +1528,7 @@
         <v>40</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1536,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D40" s="9">
         <v>18</v>
@@ -1551,7 +1551,7 @@
         <v>2</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D41" s="9">
         <v>25</v>
@@ -1565,7 +1565,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D42" s="9">
         <v>100</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B43" s="5">
         <f>SUM(B3:B42)</f>

--- a/Robot_BOM.xlsx
+++ b/Robot_BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Federico\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4235EC-7347-4AAA-85C1-68F85142283D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9208F4-B2D1-4EE4-8BDF-F3878B2D83D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1920" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t>Reference</t>
   </si>
@@ -359,14 +359,18 @@
   </si>
   <si>
     <t>https://it.aliexpress.com/item/1005006203720105.html</t>
+  </si>
+  <si>
+    <t>Totale $</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -443,7 +447,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -491,6 +495,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -795,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -806,7 +816,7 @@
     <col min="6" max="6" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="10"/>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -814,7 +824,7 @@
       <c r="E1" s="11"/>
       <c r="F1" s="11"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -833,8 +843,11 @@
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G2" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -853,8 +866,12 @@
       <c r="F3" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <f>E3*1.17</f>
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -873,8 +890,12 @@
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <f t="shared" ref="G4:G42" si="0">E4*1.17</f>
+        <v>2.0474999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -893,8 +914,12 @@
       <c r="F5" s="7" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>4.4459999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -913,8 +938,12 @@
       <c r="F6" s="7" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>1.4039999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -933,8 +962,12 @@
       <c r="F7" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>6.8327999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
@@ -953,8 +986,12 @@
       <c r="F8" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>4.0949999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -973,8 +1010,12 @@
       <c r="F9" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>7.8389999999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
@@ -993,8 +1034,12 @@
       <c r="F10" s="7" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
@@ -1013,8 +1058,12 @@
       <c r="F11" s="7" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>6.7859999999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -1033,8 +1082,12 @@
       <c r="F12" s="12" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>23.622299999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>31</v>
       </c>
@@ -1047,8 +1100,12 @@
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="12"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>33</v>
       </c>
@@ -1061,8 +1118,12 @@
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
       <c r="F14" s="12"/>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>35</v>
       </c>
@@ -1081,8 +1142,12 @@
       <c r="F15" s="7" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>10.740599999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>37</v>
       </c>
@@ -1101,8 +1166,12 @@
       <c r="F16" s="7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>12.1914</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>38</v>
       </c>
@@ -1121,8 +1190,12 @@
       <c r="F17" s="7" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>2.3984999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>39</v>
       </c>
@@ -1141,8 +1214,12 @@
       <c r="F18" s="7" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>40</v>
       </c>
@@ -1161,8 +1238,12 @@
       <c r="F19" s="12" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>41</v>
       </c>
@@ -1179,8 +1260,12 @@
         <v>2</v>
       </c>
       <c r="F20" s="16"/>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>42</v>
       </c>
@@ -1199,8 +1284,12 @@
       <c r="F21" s="17" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>5.2649999999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>43</v>
       </c>
@@ -1217,8 +1306,12 @@
         <v>5</v>
       </c>
       <c r="F22" s="16"/>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>44</v>
       </c>
@@ -1237,8 +1330,12 @@
       <c r="F23" s="17" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>46</v>
       </c>
@@ -1251,8 +1348,12 @@
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="12"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>48</v>
       </c>
@@ -1265,8 +1366,12 @@
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="12"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>50</v>
       </c>
@@ -1279,8 +1384,12 @@
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="12"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>52</v>
       </c>
@@ -1293,8 +1402,12 @@
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="16"/>
-    </row>
-    <row r="28" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>54</v>
       </c>
@@ -1313,8 +1426,12 @@
       <c r="F28" s="7" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G28">
+        <f t="shared" si="0"/>
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>55</v>
       </c>
@@ -1333,8 +1450,12 @@
       <c r="F29" s="7" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G29">
+        <f t="shared" si="0"/>
+        <v>3.4047000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>57</v>
       </c>
@@ -1353,8 +1474,12 @@
       <c r="F30" s="7" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G30">
+        <f t="shared" si="0"/>
+        <v>42.12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>59</v>
       </c>
@@ -1373,8 +1498,12 @@
       <c r="F31" s="7" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G31">
+        <f t="shared" si="0"/>
+        <v>31.589999999999996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>61</v>
       </c>
@@ -1393,8 +1522,12 @@
       <c r="F32" s="7" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G32">
+        <f t="shared" si="0"/>
+        <v>14.04</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>62</v>
       </c>
@@ -1413,8 +1546,12 @@
       <c r="F33" s="7" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G33">
+        <f t="shared" si="0"/>
+        <v>51.48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>63</v>
       </c>
@@ -1433,8 +1570,12 @@
       <c r="F34" s="7" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G34">
+        <f t="shared" si="0"/>
+        <v>24.57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>65</v>
       </c>
@@ -1453,8 +1594,12 @@
       <c r="F35" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G35">
+        <f t="shared" si="0"/>
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>68</v>
       </c>
@@ -1473,8 +1618,12 @@
       <c r="F36" s="7" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G36">
+        <f t="shared" si="0"/>
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>70</v>
       </c>
@@ -1493,8 +1642,12 @@
       <c r="F37" s="7" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G37">
+        <f t="shared" si="0"/>
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>71</v>
       </c>
@@ -1513,8 +1666,12 @@
       <c r="F38" s="7" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G38">
+        <f t="shared" si="0"/>
+        <v>2.9249999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B39" s="8">
         <v>2</v>
       </c>
@@ -1530,8 +1687,12 @@
       <c r="F39" s="12" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G39">
+        <f t="shared" si="0"/>
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B40" s="8">
         <v>1</v>
       </c>
@@ -1545,8 +1706,12 @@
         <v>18</v>
       </c>
       <c r="F40" s="12"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G40">
+        <f t="shared" si="0"/>
+        <v>21.06</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B41" s="8">
         <v>2</v>
       </c>
@@ -1559,8 +1724,12 @@
       <c r="E41" s="9">
         <v>50</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G41">
+        <f t="shared" si="0"/>
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B42" s="8">
         <v>1</v>
       </c>
@@ -1573,8 +1742,12 @@
       <c r="E42" s="9">
         <v>100</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G42">
+        <f t="shared" si="0"/>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>73</v>
       </c>
@@ -1589,6 +1762,10 @@
         <v>523.59</v>
       </c>
       <c r="F43" s="5"/>
+      <c r="G43" s="18">
+        <f>SUM(G7:G42)</f>
+        <v>612.60030000000006</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:F38" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
